--- a/Data/EXCEL/Transfer/salemon/202412/5383-salemon-202412.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202412/5383-salemon-202412.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\xls2xlsx\202412\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202412\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BB592519-92DE-4F80-8EBA-DEE12510B93A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9FB3976F-77AF-4FD8-859F-54B921A13B39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" xr2:uid="{F9AD8295-BABC-40F8-860C-8465EFDA010D}"/>
+    <workbookView xWindow="2235" yWindow="1695" windowWidth="21600" windowHeight="13425" xr2:uid="{379DD0B5-C479-4ADD-956A-0AED9D733D1F}"/>
   </bookViews>
   <sheets>
     <sheet name="5383-salemon-202412" sheetId="2" r:id="rId1"/>
@@ -1255,25 +1255,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D42C7845-08A5-4AB4-9654-BE42D5828457}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37145B11-D555-4B15-8BF1-62E69E22D077}">
   <dimension ref="A1:Q36"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.81640625" customWidth="1"/>
-    <col min="2" max="5" width="14.54296875" customWidth="1"/>
-    <col min="6" max="6" width="13.81640625" customWidth="1"/>
-    <col min="7" max="7" width="16.08984375" customWidth="1"/>
-    <col min="8" max="8" width="14.54296875" customWidth="1"/>
-    <col min="9" max="10" width="13.81640625" customWidth="1"/>
-    <col min="11" max="11" width="14.54296875" customWidth="1"/>
-    <col min="12" max="12" width="13.81640625" customWidth="1"/>
-    <col min="13" max="13" width="14.54296875" customWidth="1"/>
-    <col min="14" max="15" width="13.81640625" customWidth="1"/>
-    <col min="16" max="16" width="14.54296875" customWidth="1"/>
-    <col min="17" max="17" width="14.90625" customWidth="1"/>
+    <col min="1" max="1" width="11.875" customWidth="1"/>
+    <col min="2" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="9.5" customWidth="1"/>
+    <col min="7" max="7" width="10.875" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="10" width="9.5" customWidth="1"/>
+    <col min="11" max="11" width="10" customWidth="1"/>
+    <col min="12" max="12" width="9.5" customWidth="1"/>
+    <col min="13" max="13" width="10" customWidth="1"/>
+    <col min="14" max="15" width="9.5" customWidth="1"/>
+    <col min="16" max="16" width="10" customWidth="1"/>
+    <col min="17" max="17" width="10.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
@@ -1300,7 +1300,7 @@
       <c r="P1" s="20"/>
       <c r="Q1" s="21"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="17"/>
       <c r="B2" s="16" t="s">
         <v>4</v>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="Q2" s="21"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="17"/>
       <c r="B3" s="17"/>
       <c r="C3" s="17"/>
@@ -1382,7 +1382,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="18"/>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
@@ -1421,7 +1421,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>45383</v>
       </c>
@@ -1474,7 +1474,7 @@
         <v>-17.399999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
         <v>45352</v>
       </c>
@@ -1527,7 +1527,7 @@
         <v>-17.2</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>45323</v>
       </c>
@@ -1580,7 +1580,7 @@
         <v>-16.899999999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
         <v>45292</v>
       </c>
@@ -1633,7 +1633,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>45261</v>
       </c>
@@ -1686,7 +1686,7 @@
         <v>-21</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
         <v>45231</v>
       </c>
@@ -1739,7 +1739,7 @@
         <v>-19.399999999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>45200</v>
       </c>
@@ -1792,7 +1792,7 @@
         <v>-17.600000000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
         <v>45170</v>
       </c>
@@ -1845,7 +1845,7 @@
         <v>-15.8</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>45139</v>
       </c>
@@ -1898,7 +1898,7 @@
         <v>-14.8</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
         <v>45108</v>
       </c>
@@ -1951,7 +1951,7 @@
         <v>-16</v>
       </c>
     </row>
-    <row r="15" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>45078</v>
       </c>
@@ -2004,7 +2004,7 @@
         <v>-18.3</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
         <v>45047</v>
       </c>
@@ -2057,7 +2057,7 @@
         <v>-16.399999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>45017</v>
       </c>
@@ -2110,7 +2110,7 @@
         <v>-13.6</v>
       </c>
     </row>
-    <row r="18" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
         <v>44986</v>
       </c>
@@ -2163,7 +2163,7 @@
         <v>-14.3</v>
       </c>
     </row>
-    <row r="19" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>44958</v>
       </c>
@@ -2216,7 +2216,7 @@
         <v>-14</v>
       </c>
     </row>
-    <row r="20" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
         <v>44927</v>
       </c>
@@ -2269,7 +2269,7 @@
         <v>-36.5</v>
       </c>
     </row>
-    <row r="21" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>44896</v>
       </c>
@@ -2322,7 +2322,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="22" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
         <v>44866</v>
       </c>
@@ -2375,7 +2375,7 @@
         <v>11.2</v>
       </c>
     </row>
-    <row r="23" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>44835</v>
       </c>
@@ -2428,7 +2428,7 @@
         <v>11.4</v>
       </c>
     </row>
-    <row r="24" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
         <v>44805</v>
       </c>
@@ -2481,7 +2481,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="25" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <v>44774</v>
       </c>
@@ -2534,7 +2534,7 @@
         <v>15.5</v>
       </c>
     </row>
-    <row r="26" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
         <v>44743</v>
       </c>
@@ -2587,7 +2587,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="27" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <v>44713</v>
       </c>
@@ -2640,7 +2640,7 @@
         <v>32.5</v>
       </c>
     </row>
-    <row r="28" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="11">
         <v>44682</v>
       </c>
@@ -2693,7 +2693,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="29" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <v>44652</v>
       </c>
@@ -2746,7 +2746,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="30" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11">
         <v>44621</v>
       </c>
@@ -2799,7 +2799,7 @@
         <v>40.5</v>
       </c>
     </row>
-    <row r="31" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
         <v>44593</v>
       </c>
@@ -2852,7 +2852,7 @@
         <v>33.5</v>
       </c>
     </row>
-    <row r="32" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11">
         <v>44562</v>
       </c>
@@ -2905,7 +2905,7 @@
         <v>37.299999999999997</v>
       </c>
     </row>
-    <row r="33" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
         <v>44531</v>
       </c>
@@ -2958,7 +2958,7 @@
         <v>43.2</v>
       </c>
     </row>
-    <row r="34" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="11">
         <v>44501</v>
       </c>
@@ -3011,7 +3011,7 @@
         <v>42.4</v>
       </c>
     </row>
-    <row r="35" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
         <v>44470</v>
       </c>
@@ -3064,7 +3064,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="36" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="11">
         <v>44440</v>
       </c>
